--- a/artfynd/A 7896-2025 artfynd.xlsx
+++ b/artfynd/A 7896-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123322904</v>
+        <v>123322913</v>
       </c>
       <c r="B2" t="n">
-        <v>91397</v>
+        <v>105471</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hållnäs, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>659056</v>
+        <v>659044</v>
       </c>
       <c r="R2" t="n">
-        <v>6719569</v>
+        <v>6719554</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,35 +762,14 @@
           <t>2025-03-16</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Intorkad och ser lite otypisk ut. Väntar på validering.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -801,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123322913</v>
+        <v>123322915</v>
       </c>
       <c r="B3" t="n">
-        <v>105471</v>
+        <v>100631</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,43 +802,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hållnäs, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>659044</v>
+        <v>659056</v>
       </c>
       <c r="R3" t="n">
-        <v>6719554</v>
+        <v>6719563</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -912,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123322915</v>
+        <v>123322912</v>
       </c>
       <c r="B4" t="n">
-        <v>100631</v>
+        <v>105471</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,34 +904,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hållnäs, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>659056</v>
+        <v>659019</v>
       </c>
       <c r="R4" t="n">
-        <v>6719563</v>
+        <v>6719550</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123322912</v>
+        <v>123322914</v>
       </c>
       <c r="B5" t="n">
-        <v>105471</v>
+        <v>100631</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,43 +1015,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hållnäs, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>659019</v>
+        <v>659029</v>
       </c>
       <c r="R5" t="n">
-        <v>6719550</v>
+        <v>6719543</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1125,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123322914</v>
+        <v>123322911</v>
       </c>
       <c r="B6" t="n">
-        <v>100631</v>
+        <v>105471</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1141,34 +1117,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hållnäs, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>659029</v>
+        <v>659019</v>
       </c>
       <c r="R6" t="n">
-        <v>6719543</v>
+        <v>6719567</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,10 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123322911</v>
+        <v>123322901</v>
       </c>
       <c r="B7" t="n">
-        <v>105471</v>
+        <v>90952</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1239,47 +1224,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hållnäs, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>659019</v>
+        <v>659054</v>
       </c>
       <c r="R7" t="n">
-        <v>6719567</v>
+        <v>6719565</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,6 +1298,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1338,10 +1329,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123322901</v>
+        <v>123322904</v>
       </c>
       <c r="B8" t="n">
-        <v>90952</v>
+        <v>91397</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1350,38 +1341,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hållnäs, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>659054</v>
+        <v>659056</v>
       </c>
       <c r="R8" t="n">
-        <v>6719565</v>
+        <v>6719569</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,12 +1410,18 @@
           <t>2025-03-16</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Torkat in i ung aktiv tillväxt, innan den hunnit bli tjock.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1441,6 +1441,11 @@
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>Sten Svantesson</t>
+        </is>
+      </c>
       <c r="AW8" t="inlineStr">
         <is>
           <t>Ingemar Södergren</t>

--- a/artfynd/A 7896-2025 artfynd.xlsx
+++ b/artfynd/A 7896-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123322913</v>
       </c>
       <c r="B2" t="n">
-        <v>105471</v>
+        <v>105474</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>123322915</v>
       </c>
       <c r="B3" t="n">
-        <v>100631</v>
+        <v>100634</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123322912</v>
+        <v>123322911</v>
       </c>
       <c r="B4" t="n">
-        <v>105471</v>
+        <v>105474</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -940,7 +940,7 @@
         <v>659019</v>
       </c>
       <c r="R4" t="n">
-        <v>6719550</v>
+        <v>6719567</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123322914</v>
+        <v>123322912</v>
       </c>
       <c r="B5" t="n">
-        <v>100631</v>
+        <v>105474</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,34 +1015,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hållnäs, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>659029</v>
+        <v>659019</v>
       </c>
       <c r="R5" t="n">
-        <v>6719543</v>
+        <v>6719550</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123322911</v>
+        <v>123322901</v>
       </c>
       <c r="B6" t="n">
-        <v>105471</v>
+        <v>90955</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,47 +1122,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hållnäs, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>659019</v>
+        <v>659054</v>
       </c>
       <c r="R6" t="n">
-        <v>6719567</v>
+        <v>6719565</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,6 +1196,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1212,10 +1227,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123322901</v>
+        <v>123322914</v>
       </c>
       <c r="B7" t="n">
-        <v>90952</v>
+        <v>100634</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1224,25 +1239,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1252,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>659054</v>
+        <v>659029</v>
       </c>
       <c r="R7" t="n">
-        <v>6719565</v>
+        <v>6719543</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1298,21 +1313,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1332,7 +1332,7 @@
         <v>123322904</v>
       </c>
       <c r="B8" t="n">
-        <v>91397</v>
+        <v>91400</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 7896-2025 artfynd.xlsx
+++ b/artfynd/A 7896-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123322913</v>
+        <v>123322901</v>
       </c>
       <c r="B2" t="n">
-        <v>105474</v>
+        <v>90957</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hållnäs, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>659044</v>
+        <v>659054</v>
       </c>
       <c r="R2" t="n">
-        <v>6719554</v>
+        <v>6719565</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,6 +761,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -786,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123322915</v>
+        <v>123322911</v>
       </c>
       <c r="B3" t="n">
-        <v>100634</v>
+        <v>105476</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,34 +808,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hållnäs, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>659056</v>
+        <v>659019</v>
       </c>
       <c r="R3" t="n">
-        <v>6719563</v>
+        <v>6719567</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123322911</v>
+        <v>123322915</v>
       </c>
       <c r="B4" t="n">
-        <v>105474</v>
+        <v>100636</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,43 +919,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hållnäs, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>659019</v>
+        <v>659056</v>
       </c>
       <c r="R4" t="n">
-        <v>6719567</v>
+        <v>6719563</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123322912</v>
+        <v>123322914</v>
       </c>
       <c r="B5" t="n">
-        <v>105474</v>
+        <v>100636</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,43 +1021,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hållnäs, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>659019</v>
+        <v>659029</v>
       </c>
       <c r="R5" t="n">
-        <v>6719550</v>
+        <v>6719543</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123322901</v>
+        <v>123322913</v>
       </c>
       <c r="B6" t="n">
-        <v>90955</v>
+        <v>105476</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1122,38 +1119,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hållnäs, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>659054</v>
+        <v>659044</v>
       </c>
       <c r="R6" t="n">
-        <v>6719565</v>
+        <v>6719554</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,21 +1202,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1227,10 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123322914</v>
+        <v>123322912</v>
       </c>
       <c r="B7" t="n">
-        <v>100634</v>
+        <v>105476</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1243,34 +1234,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hållnäs, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>659029</v>
+        <v>659019</v>
       </c>
       <c r="R7" t="n">
-        <v>6719543</v>
+        <v>6719550</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,7 +1332,7 @@
         <v>123322904</v>
       </c>
       <c r="B8" t="n">
-        <v>91400</v>
+        <v>91402</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 7896-2025 artfynd.xlsx
+++ b/artfynd/A 7896-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123322901</v>
+        <v>123322915</v>
       </c>
       <c r="B2" t="n">
-        <v>90957</v>
+        <v>100642</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>659054</v>
+        <v>659056</v>
       </c>
       <c r="R2" t="n">
-        <v>6719565</v>
+        <v>6719563</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,21 +761,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -792,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123322911</v>
+        <v>123322913</v>
       </c>
       <c r="B3" t="n">
-        <v>105476</v>
+        <v>105482</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,7 +812,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -841,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>659019</v>
+        <v>659044</v>
       </c>
       <c r="R3" t="n">
-        <v>6719567</v>
+        <v>6719554</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123322915</v>
+        <v>123322901</v>
       </c>
       <c r="B4" t="n">
-        <v>100636</v>
+        <v>90963</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,25 +900,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>659056</v>
+        <v>659054</v>
       </c>
       <c r="R4" t="n">
-        <v>6719563</v>
+        <v>6719565</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,6 +974,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123322914</v>
+        <v>123322911</v>
       </c>
       <c r="B5" t="n">
-        <v>100636</v>
+        <v>105482</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,34 +1021,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hållnäs, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>659029</v>
+        <v>659019</v>
       </c>
       <c r="R5" t="n">
-        <v>6719543</v>
+        <v>6719567</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,10 +1116,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123322913</v>
+        <v>123322914</v>
       </c>
       <c r="B6" t="n">
-        <v>105476</v>
+        <v>100642</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,43 +1132,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hållnäs, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>659044</v>
+        <v>659029</v>
       </c>
       <c r="R6" t="n">
-        <v>6719554</v>
+        <v>6719543</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,7 +1221,7 @@
         <v>123322912</v>
       </c>
       <c r="B7" t="n">
-        <v>105476</v>
+        <v>105482</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>123322904</v>
       </c>
       <c r="B8" t="n">
-        <v>91402</v>
+        <v>91408</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 7896-2025 artfynd.xlsx
+++ b/artfynd/A 7896-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123322915</v>
+        <v>123322914</v>
       </c>
       <c r="B2" t="n">
-        <v>100645</v>
+        <v>100662</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>659056</v>
+        <v>659029</v>
       </c>
       <c r="R2" t="n">
-        <v>6719563</v>
+        <v>6719543</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123322901</v>
+        <v>123322911</v>
       </c>
       <c r="B3" t="n">
-        <v>90966</v>
+        <v>105502</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hållnäs, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>659054</v>
+        <v>659019</v>
       </c>
       <c r="R3" t="n">
-        <v>6719565</v>
+        <v>6719567</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -863,21 +872,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -894,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123322914</v>
+        <v>123322912</v>
       </c>
       <c r="B4" t="n">
-        <v>100645</v>
+        <v>105502</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,34 +904,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hållnäs, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>659029</v>
+        <v>659019</v>
       </c>
       <c r="R4" t="n">
-        <v>6719543</v>
+        <v>6719550</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123322911</v>
+        <v>123322901</v>
       </c>
       <c r="B5" t="n">
-        <v>105485</v>
+        <v>90983</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1008,47 +1011,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hållnäs, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>659019</v>
+        <v>659054</v>
       </c>
       <c r="R5" t="n">
-        <v>6719567</v>
+        <v>6719565</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,6 +1085,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1110,7 +1119,7 @@
         <v>123322913</v>
       </c>
       <c r="B6" t="n">
-        <v>105485</v>
+        <v>105502</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1218,10 +1227,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123322912</v>
+        <v>123322915</v>
       </c>
       <c r="B7" t="n">
-        <v>105485</v>
+        <v>100662</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1234,43 +1243,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hållnäs, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>659019</v>
+        <v>659056</v>
       </c>
       <c r="R7" t="n">
-        <v>6719550</v>
+        <v>6719563</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,7 +1332,7 @@
         <v>123322904</v>
       </c>
       <c r="B8" t="n">
-        <v>91411</v>
+        <v>91428</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 7896-2025 artfynd.xlsx
+++ b/artfynd/A 7896-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123322914</v>
+        <v>123322913</v>
       </c>
       <c r="B2" t="n">
-        <v>100662</v>
+        <v>105518</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,43 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hållnäs, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>659029</v>
+        <v>659044</v>
       </c>
       <c r="R2" t="n">
-        <v>6719543</v>
+        <v>6719554</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123322911</v>
+        <v>123322901</v>
       </c>
       <c r="B3" t="n">
-        <v>105502</v>
+        <v>90988</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,47 +798,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hållnäs, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>659019</v>
+        <v>659054</v>
       </c>
       <c r="R3" t="n">
-        <v>6719567</v>
+        <v>6719565</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,6 +872,21 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -888,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123322912</v>
+        <v>123322914</v>
       </c>
       <c r="B4" t="n">
-        <v>105502</v>
+        <v>100680</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,43 +919,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hållnäs, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>659019</v>
+        <v>659029</v>
       </c>
       <c r="R4" t="n">
-        <v>6719550</v>
+        <v>6719543</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123322901</v>
+        <v>123322915</v>
       </c>
       <c r="B5" t="n">
-        <v>90983</v>
+        <v>100680</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,25 +1017,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>659054</v>
+        <v>659056</v>
       </c>
       <c r="R5" t="n">
-        <v>6719565</v>
+        <v>6719563</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,21 +1091,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1116,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123322913</v>
+        <v>123322911</v>
       </c>
       <c r="B6" t="n">
-        <v>105502</v>
+        <v>105518</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,7 +1142,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1165,10 +1156,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>659044</v>
+        <v>659019</v>
       </c>
       <c r="R6" t="n">
-        <v>6719554</v>
+        <v>6719567</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,10 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123322915</v>
+        <v>123322912</v>
       </c>
       <c r="B7" t="n">
-        <v>100662</v>
+        <v>105518</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1243,34 +1234,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hållnäs, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>659056</v>
+        <v>659019</v>
       </c>
       <c r="R7" t="n">
-        <v>6719563</v>
+        <v>6719550</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,7 +1332,7 @@
         <v>123322904</v>
       </c>
       <c r="B8" t="n">
-        <v>91428</v>
+        <v>91433</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 7896-2025 artfynd.xlsx
+++ b/artfynd/A 7896-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123322913</v>
+        <v>123322912</v>
       </c>
       <c r="B2" t="n">
-        <v>105518</v>
+        <v>105520</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>659044</v>
+        <v>659019</v>
       </c>
       <c r="R2" t="n">
-        <v>6719554</v>
+        <v>6719550</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123322901</v>
+        <v>123322913</v>
       </c>
       <c r="B3" t="n">
-        <v>90988</v>
+        <v>105520</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,38 +798,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hållnäs, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>659054</v>
+        <v>659044</v>
       </c>
       <c r="R3" t="n">
-        <v>6719565</v>
+        <v>6719554</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,21 +881,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -903,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123322914</v>
+        <v>123322901</v>
       </c>
       <c r="B4" t="n">
-        <v>100680</v>
+        <v>90990</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>659029</v>
+        <v>659054</v>
       </c>
       <c r="R4" t="n">
-        <v>6719543</v>
+        <v>6719565</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,6 +983,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1005,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123322915</v>
+        <v>123322914</v>
       </c>
       <c r="B5" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>659056</v>
+        <v>659029</v>
       </c>
       <c r="R5" t="n">
-        <v>6719563</v>
+        <v>6719543</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1107,10 +1116,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123322911</v>
+        <v>123322915</v>
       </c>
       <c r="B6" t="n">
-        <v>105518</v>
+        <v>100682</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,43 +1132,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hållnäs, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>659019</v>
+        <v>659056</v>
       </c>
       <c r="R6" t="n">
-        <v>6719567</v>
+        <v>6719563</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,10 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123322912</v>
+        <v>123322911</v>
       </c>
       <c r="B7" t="n">
-        <v>105518</v>
+        <v>105520</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1270,7 +1270,7 @@
         <v>659019</v>
       </c>
       <c r="R7" t="n">
-        <v>6719550</v>
+        <v>6719567</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,7 +1332,7 @@
         <v>123322904</v>
       </c>
       <c r="B8" t="n">
-        <v>91433</v>
+        <v>91435</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 7896-2025 artfynd.xlsx
+++ b/artfynd/A 7896-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123322912</v>
       </c>
       <c r="B2" t="n">
-        <v>105520</v>
+        <v>105095</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123322913</v>
+        <v>123322914</v>
       </c>
       <c r="B3" t="n">
-        <v>105520</v>
+        <v>100257</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,43 +802,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hållnäs, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>659044</v>
+        <v>659029</v>
       </c>
       <c r="R3" t="n">
-        <v>6719554</v>
+        <v>6719543</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1014,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123322914</v>
+        <v>123322915</v>
       </c>
       <c r="B5" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1054,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>659029</v>
+        <v>659056</v>
       </c>
       <c r="R5" t="n">
-        <v>6719543</v>
+        <v>6719563</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1116,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123322915</v>
+        <v>123322911</v>
       </c>
       <c r="B6" t="n">
-        <v>100682</v>
+        <v>105095</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,34 +1123,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hållnäs, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>659056</v>
+        <v>659019</v>
       </c>
       <c r="R6" t="n">
-        <v>6719563</v>
+        <v>6719567</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,10 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123322911</v>
+        <v>123322913</v>
       </c>
       <c r="B7" t="n">
-        <v>105520</v>
+        <v>105095</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>659019</v>
+        <v>659044</v>
       </c>
       <c r="R7" t="n">
-        <v>6719567</v>
+        <v>6719554</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 7896-2025 artfynd.xlsx
+++ b/artfynd/A 7896-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123322912</v>
+        <v>123322915</v>
       </c>
       <c r="B2" t="n">
-        <v>105095</v>
+        <v>100257</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,43 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hållnäs, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>659019</v>
+        <v>659056</v>
       </c>
       <c r="R2" t="n">
-        <v>6719550</v>
+        <v>6719563</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123322914</v>
+        <v>123322912</v>
       </c>
       <c r="B3" t="n">
-        <v>100257</v>
+        <v>105095</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,34 +793,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hållnäs, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>659029</v>
+        <v>659019</v>
       </c>
       <c r="R3" t="n">
-        <v>6719543</v>
+        <v>6719550</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123322901</v>
+        <v>123322914</v>
       </c>
       <c r="B4" t="n">
-        <v>90990</v>
+        <v>100257</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,25 +900,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>659054</v>
+        <v>659029</v>
       </c>
       <c r="R4" t="n">
-        <v>6719565</v>
+        <v>6719543</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,21 +974,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1005,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123322915</v>
+        <v>123322901</v>
       </c>
       <c r="B5" t="n">
-        <v>100257</v>
+        <v>90990</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,25 +1002,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1045,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>659056</v>
+        <v>659054</v>
       </c>
       <c r="R5" t="n">
-        <v>6719563</v>
+        <v>6719565</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,6 +1076,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1107,7 +1107,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123322911</v>
+        <v>123322913</v>
       </c>
       <c r="B6" t="n">
         <v>105095</v>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1156,10 +1156,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>659019</v>
+        <v>659044</v>
       </c>
       <c r="R6" t="n">
-        <v>6719567</v>
+        <v>6719554</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1218,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123322913</v>
+        <v>123322911</v>
       </c>
       <c r="B7" t="n">
         <v>105095</v>
@@ -1253,7 +1253,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>659044</v>
+        <v>659019</v>
       </c>
       <c r="R7" t="n">
-        <v>6719554</v>
+        <v>6719567</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 7896-2025 artfynd.xlsx
+++ b/artfynd/A 7896-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123322915</v>
+        <v>123322914</v>
       </c>
       <c r="B2" t="n">
         <v>100257</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>659056</v>
+        <v>659029</v>
       </c>
       <c r="R2" t="n">
-        <v>6719563</v>
+        <v>6719543</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123322912</v>
+        <v>123322911</v>
       </c>
       <c r="B3" t="n">
         <v>105095</v>
@@ -812,7 +812,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -829,7 +829,7 @@
         <v>659019</v>
       </c>
       <c r="R3" t="n">
-        <v>6719550</v>
+        <v>6719567</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123322914</v>
+        <v>123322901</v>
       </c>
       <c r="B4" t="n">
-        <v>100257</v>
+        <v>90990</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,25 +900,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>659029</v>
+        <v>659054</v>
       </c>
       <c r="R4" t="n">
-        <v>6719543</v>
+        <v>6719565</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,6 +974,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -990,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123322901</v>
+        <v>123322912</v>
       </c>
       <c r="B5" t="n">
-        <v>90990</v>
+        <v>105095</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,38 +1017,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hållnäs, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>659054</v>
+        <v>659019</v>
       </c>
       <c r="R5" t="n">
-        <v>6719565</v>
+        <v>6719550</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,21 +1100,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1107,10 +1116,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123322913</v>
+        <v>123322915</v>
       </c>
       <c r="B6" t="n">
-        <v>105095</v>
+        <v>100257</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,43 +1132,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hållnäs, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>659044</v>
+        <v>659056</v>
       </c>
       <c r="R6" t="n">
-        <v>6719554</v>
+        <v>6719563</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1218,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123322911</v>
+        <v>123322913</v>
       </c>
       <c r="B7" t="n">
         <v>105095</v>
@@ -1253,7 +1253,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>659019</v>
+        <v>659044</v>
       </c>
       <c r="R7" t="n">
-        <v>6719567</v>
+        <v>6719554</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 7896-2025 artfynd.xlsx
+++ b/artfynd/A 7896-2025 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123322911</v>
+        <v>123322913</v>
       </c>
       <c r="B3" t="n">
         <v>105095</v>
@@ -812,7 +812,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>659019</v>
+        <v>659044</v>
       </c>
       <c r="R3" t="n">
-        <v>6719567</v>
+        <v>6719554</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123322912</v>
+        <v>123322915</v>
       </c>
       <c r="B5" t="n">
-        <v>105095</v>
+        <v>100257</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,43 +1021,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hållnäs, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>659019</v>
+        <v>659056</v>
       </c>
       <c r="R5" t="n">
-        <v>6719550</v>
+        <v>6719563</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1116,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123322915</v>
+        <v>123322911</v>
       </c>
       <c r="B6" t="n">
-        <v>100257</v>
+        <v>105095</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,34 +1123,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hållnäs, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>659056</v>
+        <v>659019</v>
       </c>
       <c r="R6" t="n">
-        <v>6719563</v>
+        <v>6719567</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1218,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123322913</v>
+        <v>123322912</v>
       </c>
       <c r="B7" t="n">
         <v>105095</v>
@@ -1253,7 +1253,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>659044</v>
+        <v>659019</v>
       </c>
       <c r="R7" t="n">
-        <v>6719554</v>
+        <v>6719550</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 7896-2025 artfynd.xlsx
+++ b/artfynd/A 7896-2025 artfynd.xlsx
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123322901</v>
+        <v>123322915</v>
       </c>
       <c r="B4" t="n">
-        <v>90990</v>
+        <v>100257</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,25 +900,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>659054</v>
+        <v>659056</v>
       </c>
       <c r="R4" t="n">
-        <v>6719565</v>
+        <v>6719563</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,21 +974,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1005,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123322915</v>
+        <v>123322901</v>
       </c>
       <c r="B5" t="n">
-        <v>100257</v>
+        <v>90990</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,25 +1002,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1045,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>659056</v>
+        <v>659054</v>
       </c>
       <c r="R5" t="n">
-        <v>6719563</v>
+        <v>6719565</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,6 +1076,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">

--- a/artfynd/A 7896-2025 artfynd.xlsx
+++ b/artfynd/A 7896-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123322914</v>
+        <v>123322913</v>
       </c>
       <c r="B2" t="n">
-        <v>100257</v>
+        <v>105095</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,43 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hållnäs, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>659029</v>
+        <v>659044</v>
       </c>
       <c r="R2" t="n">
-        <v>6719543</v>
+        <v>6719554</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123322913</v>
+        <v>123322915</v>
       </c>
       <c r="B3" t="n">
-        <v>105095</v>
+        <v>100257</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,43 +802,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hållnäs, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>659044</v>
+        <v>659056</v>
       </c>
       <c r="R3" t="n">
-        <v>6719554</v>
+        <v>6719563</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,7 +888,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123322915</v>
+        <v>123322914</v>
       </c>
       <c r="B4" t="n">
         <v>100257</v>
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>659056</v>
+        <v>659029</v>
       </c>
       <c r="R4" t="n">
-        <v>6719563</v>
+        <v>6719543</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123322901</v>
+        <v>123322912</v>
       </c>
       <c r="B5" t="n">
-        <v>90990</v>
+        <v>105095</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,38 +1002,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hållnäs, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>659054</v>
+        <v>659019</v>
       </c>
       <c r="R5" t="n">
-        <v>6719565</v>
+        <v>6719550</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,21 +1085,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1107,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123322911</v>
+        <v>123322901</v>
       </c>
       <c r="B6" t="n">
-        <v>105095</v>
+        <v>90990</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,47 +1113,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hållnäs, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>659019</v>
+        <v>659054</v>
       </c>
       <c r="R6" t="n">
-        <v>6719567</v>
+        <v>6719565</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,6 +1187,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1218,7 +1218,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123322912</v>
+        <v>123322911</v>
       </c>
       <c r="B7" t="n">
         <v>105095</v>
@@ -1253,7 +1253,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1270,7 +1270,7 @@
         <v>659019</v>
       </c>
       <c r="R7" t="n">
-        <v>6719550</v>
+        <v>6719567</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
